--- a/source/APPN/TD_APPN_Common.xlsx
+++ b/source/APPN/TD_APPN_Common.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -1941,7 +1941,7 @@
     <t xml:space="preserve">orcid</t>
   </si>
   <si>
-    <t xml:space="preserve">platformType</t>
+    <t xml:space="preserve">PlatformType</t>
   </si>
   <si>
     <t xml:space="preserve">brand</t>
@@ -3991,37 +3991,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -9447,7 +9447,7 @@
       <c r="K1" s="102"/>
       <c r="L1" s="102"/>
     </row>
-    <row r="2" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="104"/>
       <c r="B2" s="105"/>
       <c r="C2" s="106"/>
@@ -9461,7 +9461,7 @@
       <c r="K2" s="110"/>
       <c r="L2" s="110"/>
     </row>
-    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="111"/>
       <c r="B3" s="112"/>
       <c r="C3" s="113"/>

--- a/source/APPN/TD_APPN_Common.xlsx
+++ b/source/APPN/TD_APPN_Common.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>

--- a/source/APPN/TD_APPN_Common.xlsx
+++ b/source/APPN/TD_APPN_Common.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -1821,31 +1821,31 @@
     <t xml:space="preserve">exactMatch2</t>
   </si>
   <si>
+    <t xml:space="preserve">Plantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plants are the eukaryotic organisms that constitute the kingdom Plantae.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/NCBITaxon_33090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Plantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poaceae, also called Gramineae, is a large and nearly ubiquitous family of monocotyledonous flowering plants commonly known as true grasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://purl.obolibrary.org/obo/NCBITaxon_4479</t>
+  </si>
+  <si>
     <t xml:space="preserve">plants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plantae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plants are the eukaryotic organisms that constitute the kingdom Plantae.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.obolibrary.org/obo/NCBITaxon_33090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.wikipedia.org/wiki/Plantae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poaceae, also called Gramineae, is a large and nearly ubiquitous family of monocotyledonous flowering plants commonly known as true grasses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://purl.obolibrary.org/obo/NCBITaxon_4479</t>
   </si>
   <si>
     <t xml:space="preserve">https://en.wikipedia.org/wiki/Poaceae</t>
@@ -8833,40 +8833,40 @@
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>390</v>
+        <v>48</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
       <c r="D2" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" s="46" t="s">
         <v>391</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="G2" s="57" t="s">
         <v>392</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="I2" s="47" t="s">
         <v>393</v>
-      </c>
-      <c r="I2" s="47" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="46" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="G3" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="H3" s="46" t="s">
         <v>398</v>
-      </c>
-      <c r="H3" s="46" t="s">
-        <v>390</v>
       </c>
       <c r="I3" s="47" t="s">
         <v>399</v>
@@ -8892,7 +8892,7 @@
         <v>405</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I4" s="47" t="s">
         <v>406</v>
@@ -8918,7 +8918,7 @@
         <v>412</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I5" s="47" t="s">
         <v>413</v>
@@ -8944,7 +8944,7 @@
         <v>419</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="I6" s="47" t="s">
         <v>420</v>
@@ -8970,7 +8970,7 @@
         <v>426</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="I7" s="47" t="s">
         <v>427</v>
